--- a/data/爱乐之城-表演道具验证配置-V2.1.xlsx
+++ b/data/爱乐之城-表演道具验证配置-V2.1.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" r:id="Rb601f4e88c4245f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="规则配置" sheetId="2" r:id="Rf758400649c7422c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品质配置" sheetId="3" r:id="R8ed5e65dddf549d1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="套装配置" sheetId="4" r:id="R13f934d709db42f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="道具配置" sheetId="5" r:id="R6668194976754867"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表演规则" sheetId="6" r:id="Re4742095daff4fb2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="发挥档位" sheetId="7" r:id="R000e8415e6774cff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="现场事件" sheetId="8" r:id="Rf8afb7776ca942ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="种类表演特性" sheetId="9" r:id="R707b3a7f2130426d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" r:id="R24c09266540245c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="规则配置" sheetId="2" r:id="Ra3b55a6e9bab4e01"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品质配置" sheetId="3" r:id="R93ac643f8a634c8f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="套装配置" sheetId="4" r:id="Rf8409dc600894938"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="道具配置" sheetId="5" r:id="R97c025125d534ffb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表演规则" sheetId="6" r:id="R3878f58088d74c6e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="发挥档位" sheetId="7" r:id="R79c1932b7f0c4846"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="现场事件" sheetId="8" r:id="R325407e0a0684ca3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="种类表演特性" sheetId="9" r:id="R12d017e652454273"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -830,8 +830,11 @@
     </x:row>
     <x:row r="2" ht="34" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>黄色值为主要可调参数；V2.1将扩格与同品质道具三选一分开结算。</x:v>
-      </x:c>
+        <x:v>黄色值为主要可调参数；三选一先确定道具品质，扩格选项按概率替代其中1个道具位。</x:v>
+      </x:c>
+      <x:c r="B2"/>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="14" t="str">
@@ -1048,13 +1051,13 @@
         <x:v>reward_unlock_option_chance</x:v>
       </x:c>
       <x:c r="B19" s="41" t="n">
-        <x:v>0</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="C19" s="25" t="str">
         <x:v>小数</x:v>
       </x:c>
       <x:c r="D19" s="25" t="str">
-        <x:v>三选一固定展示3件同品质道具，不插入扩格选项</x:v>
+        <x:v>三选一中出现扩展格子选项的概率（0—1，可配置）</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -1132,13 +1135,13 @@
         <x:v>reward_unlock_grant_chance</x:v>
       </x:c>
       <x:c r="B25" s="46" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C25" s="45" t="str">
         <x:v>小数</x:v>
       </x:c>
       <x:c r="D25" s="45" t="str">
-        <x:v>进入奖励时独立获得扩格机会的概率</x:v>
+        <x:v>兼容旧配置；当前不在奖励选择外额外发放扩格机会</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -1152,7 +1155,7 @@
         <x:v>布尔</x:v>
       </x:c>
       <x:c r="D26" s="45" t="str">
-        <x:v>每组三选一先抽品质，再在该品质池中抽3件不同道具</x:v>
+        <x:v>同一组三选一中出现的全部道具选项使用同一品质</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -1196,7 +1199,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R899584e6ad534329"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d9cc4ba7281492b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1335,7 +1338,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R87acd338d3ad48b0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2281fedf787f4cc1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1594,7 +1597,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf8569d68a56488b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3fb4c533df1f4c3f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6142,7 +6145,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R923fe8bd142a45bb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R71a6723d93b042c6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6345,7 +6348,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R758b73940e9a4e7e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1ffa1070415c45d9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6464,7 +6467,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rba41560dd0594ccd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd5a36932bda84aa2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6637,7 +6640,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9db624c6da9843d3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R948fb209e3ef414c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6756,7 +6759,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R27a4f409956a49fc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re1f24313f8fb4916"/>
   </x:tableParts>
 </x:worksheet>
 </file>